--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45922.48036304351</v>
+        <v>45927.88381204757</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45923.48036304351</v>
+        <v>45928.88381204757</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45924.48036304351</v>
+        <v>45929.88381204757</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45922.48036304351</v>
+        <v>45927.78789245197</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45923.48036304351</v>
+        <v>45928.78789246629</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45924.48036304351</v>
+        <v>45929.78789246635</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45927.88381204757</v>
+        <v>45930.97170014358</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45928.88381204757</v>
+        <v>45931.97170016574</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45929.88381204757</v>
+        <v>45932.97170016582</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45930.97170014358</v>
+        <v>45931.78274439334</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45931.97170016574</v>
+        <v>45932.78274440008</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45932.97170016582</v>
+        <v>45933.78274440016</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45931.78274439334</v>
+        <v>45932.05822198468</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45932.78274440008</v>
+        <v>45933.05822198468</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45933.78274440016</v>
+        <v>45934.05822198468</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45932.05822198468</v>
+        <v>45932.43856581674</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45933.05822198468</v>
+        <v>45933.43856582479</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45934.05822198468</v>
+        <v>45934.43856582483</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45932.43856581674</v>
+        <v>45933.48265763497</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45933.43856582479</v>
+        <v>45934.48265763573</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45934.43856582483</v>
+        <v>45935.48265763577</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/sample_template.xlsx
+++ b/sample_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45933.48265763497</v>
+        <v>45964.99145891708</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45934.48265763573</v>
+        <v>45965.99145891708</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45935.48265763577</v>
+        <v>45966.99145891708</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
